--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/farris.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/farris.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="farris" sheetId="1" r:id="rId3"/>
+    <sheet name="farris" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="190">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -402,7 +402,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Eek!</t>
@@ -736,246 +736,6 @@
     <t xml:space="preserve">Demitas, the Exile... I wonder what he was like before he became...
 And what caused him to be exiled in the first place? One day, I’d love to hear his story from him.</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你好，#player大人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜…呜呜…谁来…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜呜…谁…谁在那里？　</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦哦…感谢仁慈的艾赫卡托尔赐予的机缘。
-我是奥尔维纳的歌手法莉斯。因为注意到了尼米尔的异变，雇佣冒险者一同来到这个洞穴，结果被凶暴化的魔物袭击陷入进退两难的地步。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">作为将米西利亚传说传唱之人，我必须知道这片土地上发生了什么。但是，在这样的情况下，我只能回头……
-如果您还要继续前进的话，就把这条通道的钥匙交给您吧。我希望您能查明尼米尔深处的异变。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">唉…附近有您的营地吗？
-我明白了。那我就暂且返回营地等您的消息。探索顺利完成后请跟我打声招呼。我有些话想跟您说。
-冒险家大人，祈愿您能平安归来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">您平安回来了呢。
-再次介绍…我是奥尔维娜的法莉斯，咏唱古老传说之人。就让我告诉您我所知道的一切关于尼米尔的事作为对您的报答吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">尼米尔…是提里斯上散落的遗迹之一，也是被称为风之墓场的洞窟。正如其名所述，这是一个回荡着悲哀风鸣的安稳洞窟……应该说…曾经是这样的。因为在十年战争之后，尼米尔就变了……
-尼米尔的森林开始枯萎，不再有风声，异形的魔物开始在地上徘徊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">异变的原因…尼米尔的深层到底发生了什么呢？
-据传闻说，在洞窟的最下层沉睡着被遗忘众神的圣遗物。也许…我们是招来了古老神明的愤怒…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―不，供奉在尼米尔最深处的并不是贵重的圣遗物，异变的原因也不是作祟。
-不好意思打断你讲话了。但是，那个洞窟的情况果然是和我们想的一样…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阿什！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没事的，菲亚。让我说吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…十年战争和尼米尔的异变不是没有关系的。
-上次大战的事恐怕你也听说过了。东大陆，新王国耶鲁和沙漠帝国发起的战火不久便燃向各地，给世界带来了混乱。提里斯的国家也结成联盟进行了对抗，但在拥有萨伊拉飞艇的帝国面前简直就和婴儿一样。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在我们的土地被践踏的时候，我们的主公赛特拉斯大人对风诉说。结果尼米尔的天空中出现的一阵光之风化成的风暴袭击了帝国，被誉为无敌的萨伊拉的飞艇坠落到了米西利亚的土地上。
-…然后十年战争迎来了终结。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">唤起「尼米尔狂风」的确实是赛特拉斯大人。但是，仅此而已吗？
-米西利亚刮起的光之风和尼米尔的异变之间，或许就是沉睡在被称为风之墓地尼米尔的「某物」回应了赛特拉斯大人的祈祷所致。
-我推测，那个神秘「某物」就藏在尼米尔的最深处。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现在阴云即将再次笼罩提里斯之上。
-帝国在重新磨锐折断的利爪，萨伊拉的舰队重建只是时间问题。在下一场战斗中，他们一定会为一雪前耻毫不留情地进行攻击。
-赛特拉斯大人对人类和艾莱亚的重新团结抱有希望，但如果米西利亚灭亡，那一切就无从说起了。为了生存，我们必须得到沉睡在尼米尔中的「力量」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…现在还不能说出一切，我们也并不了解一切。你一定会觉得是被卷入了麻烦的事情中吧。
-但是，你已经在此地定居，成为了米西利亚和提里斯的一员，这件事情和你也就并不是没有关系。
-所以呢，你就做好心理准备配合我们的调查吧。山洞里面也可能会有一两个宝贝，对你来说也不是坏事。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…话就说到这里吧。
-尼米尔的异变于我来说也不是毫无关系。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我打算暂时留在这里，观察事情的发展。
-冒险家大人，祝你武运亨通。希望你前进的道路上有风的加护。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#player大人，我有话跟您说。
-关于利萨纳斯，我也有线索。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的妹妹西奥露西亚在帕罗米亚王宫工作，从事历史研究。
-如果是她的话，一定可以从王宫图书馆所有的庞大资料中找到关于利萨纳斯的文献。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">从这里沿着路向西南方向走，有一个叫奥尔维纳的小村庄…那是我的故乡。
-西奥露西亚现在也应该回到村子里了。如果#player大人正在寻找利萨纳斯的线索，也许你可以去拜访她一次。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（嘀嘀咕咕）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">果然是…（嘀嘀咕咕）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊…！（嘀嘀咕咕）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你好啊，法莉斯小姐。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊，罗伊特尔大人。库罗茨亚正和我说到您的事情呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">噫。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊，不是……啊，库罗茨亚你要去哪里……等等啊……！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…罗伊特尔大人，对待这个年纪的少女，可不能看着人家的脸发出「噫」的声音啊…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不，我没有那样的意思！
-…只是，我想起了那个孩子眼睛的事情。法莉斯小姐也从凯特尔那里听说了吧？我被那个孩子讨厌了……没准哪天就突然没命了…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…罗伊特尔大人啊，我对你真是太失望了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明明不了解她拥有怎样的力量，却断言那是「诅咒」并恐惧着她…你难道不明白，这样的态度才最伤她的心吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没有什么但是！在害怕「诅咒」之前，你应该多想想那孩子与怎样的孤独战斗过。无论她有怎样的瞳色和过去，她也只是个少女。她也有心啊，罗伊特尔大人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法莉斯小姐…的确如你所言。
-其实，我也想和那个孩子好好相处。但却总是言多语失…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…库罗茨亚是个心思细腻老实的孩子。罗伊特尔大人是不是因为怕伤害到她而顾忌太多，才让事情毫无进展？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凡事都有过程。那些故事里的主人公们也是克服彼此间的隔阂才能建立真正相互信赖的关系。
-您知道吗，罗伊特尔大人。如果您想打开她的心扉，就必须用尽办法去直面她，引她说出真实的心声，然后全心全意地接纳她袒露出的灵魂呼喊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">唔…嗯，感觉有点夸张，但我明白你的意思，法莉斯小姐。
-要引出库罗茨亚的心声吗…哎呀，这可真是个挑战呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#pc大人，您来的正好。
-那个…其实是这样，事情也过去这么久了，一直都没看到罗伊特尔大人有在还债的样子，大伙都想问问您的情况如何。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">罗伊特尔大人，请告诉我们…您宏伟的还债计划！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法莉斯小姐…根本就没有计划。
-…两千万奥伦这种荒唐的金额，我怎么还得起！ 我…我…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊！ 罗伊特尔大人！？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大家，罗伊特尔大人逃走了…！ 快，快点，抓住罗伊特尔大人！ 喂，凯特尔先生，您也快去追他！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯…好吧…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哈啊哈啊，可恶…怎么能让你们抓住我！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哈，这可是在开拓中锻炼出来的腰腿。只要我全力逃跑，区区女人和孩子…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…呜噶啊！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">歌罗贡，真是个好孩子！就这样拖住罗伊特尔！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哈啊…哈啊…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">快放弃吧，罗伊特尔。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你们…竟然联手…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">行吧行吧，其实我是有个还没完成的还款计划！
-我现在就去拿…请在这里等我。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊！ 罗伊特尔大人！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…逃跑…了呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然我觉得罗伊特尔大人即使身处困境也应该不会做出什么极端的行为…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但还是很担心呢。
-#pc大人，如果您对罗伊特尔大人的逃亡目的地有线索的话，能帮我找他吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（窃窃私语）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">唔…（窃窃私语）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的意思是…（窃窃私语）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">什么，居然…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真是的，自从那个迪米塔斯来了之后，气氛一直都很沉重。库罗茨亚也变得不愿意说话了。
-他总是说些让人不安的话，真是让人头疼啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是罗伊特尔大人，我觉得他并不是什么坏人。迪米塔斯先生应该只是有心病吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯，心病？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">虽然不能确信。但是，迪米塔斯先生的内心应该有些扭曲…
-那种诡异说话方式的背后，不知隐藏了多少苦恼和悲伤…真的让人很感兴趣。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…说起来，法莉斯小姐看着迪米塔斯时，眼神总是闪闪发光。
-他确实令人不快，但给人的印象并非纯粹的恶徒。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">流放者迪米塔斯…变成这样之前，他究竟是怎样的人呢。我也想知道他被「流放」的原因。
-…总有一天，我要听他本人来讲讲。</t>
-  </si>
 </sst>
 </file>
 
@@ -996,19 +756,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1028,7 +788,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1054,7 +814,7 @@
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -1073,7 +833,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -1082,94 +842,94 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1183,13 +943,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1365,24 +1125,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M160"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="3" width="8.85" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
-    <col min="9" max="9" width="63.3" style="1" customWidth="1"/>
-    <col min="10" max="10" width="53.28" style="1" customWidth="1"/>
-    <col min="11" max="11" width="73.45" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="63.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="73.45"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1417,13 +1177,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H5:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H5:H1048576)</f>
         <v>89</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1431,7 +1191,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1439,18 +1199,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
-      <c r="H12" s="1">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="1" t="n">
         <v>49</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -1459,11 +1219,8 @@
       <c r="J12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" ht="12.8">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1471,28 +1228,28 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
-      <c r="H20" s="1">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -1501,22 +1258,19 @@
       <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K20" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="21" ht="12.8">
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" ht="12.8">
-      <c r="H23" s="1">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -1525,12 +1279,9 @@
       <c r="J23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" ht="64.15">
-      <c r="H24" s="1">
+    </row>
+    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I24" s="3" t="s">
@@ -1539,11 +1290,8 @@
       <c r="J24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K24" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="25" ht="12.8">
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1553,8 +1301,8 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" ht="64.15">
-      <c r="H26" s="1">
+    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -1563,12 +1311,9 @@
       <c r="J26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" ht="64.15">
-      <c r="H27" s="1">
+    </row>
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I27" s="3" t="s">
@@ -1577,11 +1322,8 @@
       <c r="J27" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K27" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="28" ht="12.8">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="1" t="s">
         <v>37</v>
       </c>
@@ -1589,18 +1331,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" ht="53.7">
-      <c r="H31" s="1">
+    <row r="31" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -1609,12 +1351,9 @@
       <c r="J31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K31" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" ht="95.5">
-      <c r="H32" s="1">
+    </row>
+    <row r="32" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -1623,12 +1362,9 @@
       <c r="J32" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="K32" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" ht="64.15">
-      <c r="H33" s="1">
+    </row>
+    <row r="33" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I33" s="3" t="s">
@@ -1637,11 +1373,8 @@
       <c r="J33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="34" ht="12.8">
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="1" t="s">
         <v>46</v>
       </c>
@@ -1649,11 +1382,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" ht="53.7">
+    <row r="35" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I35" s="3" t="s">
@@ -1662,15 +1395,12 @@
       <c r="J35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K35" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36" ht="12.8">
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F36" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -1679,15 +1409,12 @@
       <c r="J36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K36" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="37" ht="12.8">
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -1696,11 +1423,8 @@
       <c r="J37" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K37" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="38" ht="12.8">
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="1" t="s">
         <v>54</v>
       </c>
@@ -1708,11 +1432,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" ht="116.4">
+    <row r="39" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F39" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
@@ -1721,15 +1445,12 @@
       <c r="J39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K39" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="40" ht="74.6">
+    </row>
+    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I40" s="3" t="s">
@@ -1738,15 +1459,12 @@
       <c r="J40" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K40" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" ht="95.5">
+    </row>
+    <row r="41" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I41" s="3" t="s">
@@ -1755,15 +1473,12 @@
       <c r="J41" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="K41" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="42" ht="105.95">
+    </row>
+    <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -1772,15 +1487,12 @@
       <c r="J42" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K42" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="43" ht="95.5">
+    </row>
+    <row r="43" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F43" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I43" s="3" t="s">
@@ -1789,11 +1501,8 @@
       <c r="J43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K43" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="44" ht="12.8">
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="1" t="s">
         <v>66</v>
       </c>
@@ -1801,7 +1510,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="1" t="s">
         <v>68</v>
       </c>
@@ -1809,8 +1518,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" ht="32.8">
-      <c r="H47" s="1">
+    <row r="47" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I47" s="3" t="s">
@@ -1819,12 +1528,9 @@
       <c r="J47" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K47" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="48" ht="43.25">
-      <c r="H48" s="1">
+    </row>
+    <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I48" s="3" t="s">
@@ -1833,11 +1539,8 @@
       <c r="J48" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K48" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="49" ht="12.8">
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="1" t="s">
         <v>46</v>
       </c>
@@ -1845,7 +1548,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="1" t="s">
         <v>37</v>
       </c>
@@ -1853,50 +1556,41 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="57" ht="12.8">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" ht="32.8">
-      <c r="H61" s="1">
+    <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="1" t="n">
         <v>19</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="K61" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="62" ht="43.25">
-      <c r="H62" s="1">
+    </row>
+    <row r="62" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H62" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K62" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="63" ht="53.7">
-      <c r="H63" s="1">
+    </row>
+    <row r="63" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H63" s="1" t="n">
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="K63" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="65" ht="12.8">
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D65" s="1" t="s">
         <v>78</v>
       </c>
@@ -1904,18 +1598,18 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" ht="12.8">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D67" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="69" ht="12.8">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D70" s="1" t="s">
         <v>11</v>
       </c>
@@ -1924,7 +1618,7 @@
       </c>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" ht="12.8">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D71" s="1" t="s">
         <v>11</v>
       </c>
@@ -1933,7 +1627,7 @@
       </c>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" ht="12.8">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D72" s="1" t="s">
         <v>78</v>
       </c>
@@ -1942,19 +1636,19 @@
       </c>
       <c r="L72" s="1"/>
     </row>
-    <row r="73" ht="13.8">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D73" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="1" t="n">
         <v>74</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="7"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" ht="13.8">
-      <c r="H74" s="6">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="6" t="n">
         <v>22</v>
       </c>
       <c r="I74" s="8" t="s">
@@ -1963,16 +1657,14 @@
       <c r="J74" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K74" s="7" t="s">
-        <v>213</v>
-      </c>
+      <c r="K74" s="7"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" ht="13.8">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F75" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H75" s="6">
+      <c r="H75" s="6" t="n">
         <v>23</v>
       </c>
       <c r="I75" s="8" t="s">
@@ -1981,13 +1673,11 @@
       <c r="J75" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K75" s="7" t="s">
-        <v>213</v>
-      </c>
+      <c r="K75" s="7"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" ht="13.8">
-      <c r="H76" s="6">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H76" s="6" t="n">
         <v>24</v>
       </c>
       <c r="I76" s="8" t="s">
@@ -1996,16 +1686,14 @@
       <c r="J76" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="K76" s="7" t="s">
-        <v>214</v>
-      </c>
+      <c r="K76" s="7"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" ht="13.8">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F77" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H77" s="6">
+      <c r="H77" s="6" t="n">
         <v>25</v>
       </c>
       <c r="I77" s="8" t="s">
@@ -2014,13 +1702,11 @@
       <c r="J77" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K77" s="7" t="s">
-        <v>213</v>
-      </c>
+      <c r="K77" s="7"/>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" ht="13.8">
-      <c r="H78" s="6">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H78" s="6" t="n">
         <v>26</v>
       </c>
       <c r="I78" s="8" t="s">
@@ -2029,16 +1715,14 @@
       <c r="J78" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="K78" s="7" t="s">
-        <v>215</v>
-      </c>
+      <c r="K78" s="7"/>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" ht="13.8">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F79" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H79" s="6">
+      <c r="H79" s="6" t="n">
         <v>27</v>
       </c>
       <c r="I79" s="8" t="s">
@@ -2047,13 +1731,11 @@
       <c r="J79" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="K79" s="7" t="s">
-        <v>216</v>
-      </c>
+      <c r="K79" s="7"/>
       <c r="L79" s="1"/>
     </row>
-    <row r="80" ht="25.35">
-      <c r="H80" s="11">
+    <row r="80" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="11" t="n">
         <v>28</v>
       </c>
       <c r="I80" s="12" t="s">
@@ -2062,16 +1744,14 @@
       <c r="J80" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="K80" s="3" t="s">
-        <v>217</v>
-      </c>
+      <c r="K80" s="3"/>
       <c r="L80" s="1"/>
     </row>
-    <row r="81" ht="13.8">
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F81" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H81" s="1">
+      <c r="H81" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I81" s="12" t="s">
@@ -2080,16 +1760,14 @@
       <c r="J81" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="K81" s="3"/>
       <c r="L81" s="1"/>
     </row>
-    <row r="82" ht="13.8">
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F82" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H82" s="1">
+      <c r="H82" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="12" t="s">
@@ -2098,16 +1776,14 @@
       <c r="J82" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="K82" s="7" t="s">
-        <v>218</v>
-      </c>
+      <c r="K82" s="7"/>
       <c r="L82" s="1"/>
     </row>
-    <row r="83" ht="13.8">
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F83" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H83" s="1">
+      <c r="H83" s="1" t="n">
         <v>31</v>
       </c>
       <c r="I83" s="12" t="s">
@@ -2116,16 +1792,14 @@
       <c r="J83" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="K83" s="3"/>
       <c r="L83" s="1"/>
     </row>
-    <row r="84" ht="13.8">
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F84" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H84" s="1" t="n">
         <v>32</v>
       </c>
       <c r="I84" s="12" t="s">
@@ -2134,14 +1808,12 @@
       <c r="J84" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="K84" s="3" t="s">
-        <v>219</v>
-      </c>
+      <c r="K84" s="3"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
     </row>
-    <row r="85" ht="13.8">
-      <c r="H85" s="1">
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H85" s="1" t="n">
         <v>33</v>
       </c>
       <c r="I85" s="12" t="s">
@@ -2150,16 +1822,14 @@
       <c r="J85" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="K85" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="K85" s="3"/>
       <c r="L85" s="1"/>
     </row>
-    <row r="86" ht="13.8">
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F86" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H86" s="1" t="n">
         <v>34</v>
       </c>
       <c r="I86" s="12" t="s">
@@ -2168,13 +1838,11 @@
       <c r="J86" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K86" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="K86" s="3"/>
       <c r="L86" s="1"/>
     </row>
-    <row r="87" ht="13.8">
-      <c r="H87" s="1">
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H87" s="1" t="n">
         <v>35</v>
       </c>
       <c r="I87" s="8" t="s">
@@ -2183,16 +1851,14 @@
       <c r="J87" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="K87" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="K87" s="3"/>
       <c r="L87" s="1"/>
     </row>
-    <row r="88" ht="57.45">
+    <row r="88" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F88" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H88" s="1" t="n">
         <v>36</v>
       </c>
       <c r="I88" s="8" t="s">
@@ -2201,13 +1867,11 @@
       <c r="J88" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="K88" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="K88" s="3"/>
       <c r="L88" s="1"/>
     </row>
-    <row r="89" ht="13.8">
-      <c r="H89" s="1">
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H89" s="1" t="n">
         <v>37</v>
       </c>
       <c r="I89" s="8" t="s">
@@ -2216,13 +1880,11 @@
       <c r="J89" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>222</v>
-      </c>
+      <c r="K89" s="3"/>
       <c r="L89" s="1"/>
     </row>
-    <row r="90" ht="35.05">
-      <c r="H90" s="1">
+    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H90" s="1" t="n">
         <v>38</v>
       </c>
       <c r="I90" s="8" t="s">
@@ -2231,16 +1893,14 @@
       <c r="J90" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K90" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="K90" s="3"/>
       <c r="L90" s="1"/>
     </row>
-    <row r="91" ht="13.8">
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F91" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H91" s="1" t="n">
         <v>39</v>
       </c>
       <c r="I91" s="8" t="s">
@@ -2249,13 +1909,11 @@
       <c r="J91" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>224</v>
-      </c>
+      <c r="K91" s="3"/>
       <c r="L91" s="1"/>
     </row>
-    <row r="92" ht="35.05">
-      <c r="H92" s="1">
+    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H92" s="1" t="n">
         <v>40</v>
       </c>
       <c r="I92" s="8" t="s">
@@ -2264,16 +1922,14 @@
       <c r="J92" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="K92" s="3" t="s">
-        <v>225</v>
-      </c>
+      <c r="K92" s="3"/>
       <c r="L92" s="1"/>
     </row>
-    <row r="93" ht="46.25">
+    <row r="93" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F93" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H93" s="1" t="n">
         <v>41</v>
       </c>
       <c r="I93" s="8" t="s">
@@ -2282,20 +1938,18 @@
       <c r="J93" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="K93" s="3" t="s">
-        <v>226</v>
-      </c>
+      <c r="K93" s="3"/>
       <c r="L93" s="1"/>
     </row>
-    <row r="94" ht="13.8">
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F94" s="3"/>
       <c r="I94" s="8"/>
       <c r="J94" s="10"/>
       <c r="K94" s="3"/>
       <c r="L94" s="1"/>
     </row>
-    <row r="95" ht="23.85">
-      <c r="H95" s="1">
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H95" s="1" t="n">
         <v>43</v>
       </c>
       <c r="I95" s="8" t="s">
@@ -2304,13 +1958,11 @@
       <c r="J95" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="K95" s="3" t="s">
-        <v>227</v>
-      </c>
+      <c r="K95" s="3"/>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" ht="69.4">
-      <c r="H96" s="1">
+    <row r="96" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H96" s="1" t="n">
         <v>48</v>
       </c>
       <c r="I96" s="8" t="s">
@@ -2319,16 +1971,14 @@
       <c r="J96" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>228</v>
-      </c>
+      <c r="K96" s="3"/>
       <c r="L96" s="1"/>
     </row>
-    <row r="97" ht="56.7">
+    <row r="97" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F97" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H97" s="1">
+      <c r="H97" s="1" t="n">
         <v>44</v>
       </c>
       <c r="I97" s="8" t="s">
@@ -2337,16 +1987,14 @@
       <c r="J97" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="K97" s="3" t="s">
-        <v>229</v>
-      </c>
+      <c r="K97" s="3"/>
       <c r="L97" s="1"/>
     </row>
-    <row r="98" ht="13.8">
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D98" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I98" s="6"/>
@@ -2354,28 +2002,28 @@
       <c r="K98" s="7"/>
       <c r="L98" s="1"/>
     </row>
-    <row r="99" ht="12.8">
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D99" s="1" t="s">
         <v>122</v>
       </c>
       <c r="L99" s="1"/>
     </row>
-    <row r="100" ht="12.8">
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D100" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L100" s="1"/>
     </row>
-    <row r="101" ht="12.8">
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L101" s="1"/>
     </row>
-    <row r="102" ht="12.8">
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>123</v>
       </c>
       <c r="L102" s="1"/>
     </row>
-    <row r="103" ht="12.8">
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="1" t="s">
         <v>11</v>
       </c>
@@ -2384,7 +2032,7 @@
       </c>
       <c r="L103" s="1"/>
     </row>
-    <row r="104" s="1" customFormat="1" ht="12.8">
+    <row r="104" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -2401,7 +2049,7 @@
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
     </row>
-    <row r="105" s="1" customFormat="1" ht="12.8">
+    <row r="105" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -2418,7 +2066,7 @@
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
     </row>
-    <row r="106" s="1" customFormat="1" ht="12.8">
+    <row r="106" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -2435,7 +2083,7 @@
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
     </row>
-    <row r="107" ht="12.8">
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="1" t="s">
         <v>78</v>
       </c>
@@ -2444,20 +2092,20 @@
       </c>
       <c r="L107" s="1"/>
     </row>
-    <row r="108" ht="13.8">
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E108" s="1" t="n">
         <v>72</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108" s="7"/>
       <c r="L108" s="1"/>
     </row>
-    <row r="109" ht="49.25">
+    <row r="109" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F109" s="3"/>
-      <c r="H109" s="1">
+      <c r="H109" s="1" t="n">
         <v>50</v>
       </c>
       <c r="I109" s="12" t="s">
@@ -2466,14 +2114,12 @@
       <c r="J109" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="K109" s="3" t="s">
-        <v>230</v>
-      </c>
+      <c r="K109" s="3"/>
       <c r="L109" s="1"/>
     </row>
-    <row r="110" ht="23.85">
+    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F110" s="3"/>
-      <c r="H110" s="1">
+      <c r="H110" s="1" t="n">
         <v>51</v>
       </c>
       <c r="I110" s="8" t="s">
@@ -2482,16 +2128,14 @@
       <c r="J110" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K110" s="3" t="s">
-        <v>231</v>
-      </c>
+      <c r="K110" s="3"/>
       <c r="L110" s="1"/>
     </row>
-    <row r="111" ht="13.8">
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F111" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H111" s="1">
+      <c r="H111" s="1" t="n">
         <v>52</v>
       </c>
       <c r="I111" s="8" t="s">
@@ -2500,16 +2144,14 @@
       <c r="J111" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K111" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="K111" s="3"/>
       <c r="L111" s="1"/>
     </row>
-    <row r="112" ht="45.5">
+    <row r="112" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F112" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H112" s="1">
+      <c r="H112" s="1" t="n">
         <v>53</v>
       </c>
       <c r="I112" s="8" t="s">
@@ -2518,12 +2160,10 @@
       <c r="J112" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="K112" s="3" t="s">
-        <v>232</v>
-      </c>
+      <c r="K112" s="3"/>
       <c r="L112" s="1"/>
     </row>
-    <row r="113" ht="13.8">
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="1" t="s">
         <v>134</v>
       </c>
@@ -2531,19 +2171,17 @@
         <v>135</v>
       </c>
       <c r="F113" s="3"/>
-      <c r="H113" s="1">
+      <c r="H113" s="1" t="n">
         <v>54</v>
       </c>
       <c r="I113" s="11"/>
       <c r="J113" s="10"/>
-      <c r="K113" s="3" t="s">
-        <v>190</v>
-      </c>
+      <c r="K113" s="3"/>
       <c r="L113" s="1"/>
     </row>
-    <row r="114" ht="13.8">
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F114" s="3"/>
-      <c r="H114" s="1">
+      <c r="H114" s="1" t="n">
         <v>55</v>
       </c>
       <c r="I114" s="6" t="s">
@@ -2552,14 +2190,12 @@
       <c r="J114" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="K114" s="3" t="s">
-        <v>233</v>
-      </c>
+      <c r="K114" s="3"/>
       <c r="L114" s="1"/>
     </row>
-    <row r="115" ht="23.85">
+    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F115" s="3"/>
-      <c r="H115" s="1">
+      <c r="H115" s="1" t="n">
         <v>56</v>
       </c>
       <c r="I115" s="8" t="s">
@@ -2568,16 +2204,14 @@
       <c r="J115" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="K115" s="3" t="s">
-        <v>234</v>
-      </c>
+      <c r="K115" s="3"/>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" ht="13.8">
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F116" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H116" s="1">
+      <c r="H116" s="1" t="n">
         <v>57</v>
       </c>
       <c r="I116" s="6" t="s">
@@ -2586,16 +2220,14 @@
       <c r="J116" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="K116" s="3" t="s">
-        <v>235</v>
-      </c>
+      <c r="K116" s="3"/>
       <c r="L116" s="1"/>
     </row>
-    <row r="117" ht="13.8">
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F117" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H117" s="1">
+      <c r="H117" s="1" t="n">
         <v>58</v>
       </c>
       <c r="I117" s="6" t="s">
@@ -2604,16 +2236,14 @@
       <c r="J117" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="K117" s="3" t="s">
-        <v>236</v>
-      </c>
+      <c r="K117" s="3"/>
       <c r="L117" s="1"/>
     </row>
-    <row r="118" ht="23.85">
+    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F118" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H118" s="1">
+      <c r="H118" s="1" t="n">
         <v>59</v>
       </c>
       <c r="I118" s="6" t="s">
@@ -2622,12 +2252,10 @@
       <c r="J118" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="K118" s="3" t="s">
-        <v>237</v>
-      </c>
+      <c r="K118" s="3"/>
       <c r="L118" s="1"/>
     </row>
-    <row r="119" ht="13.8">
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="1" t="s">
         <v>134</v>
       </c>
@@ -2640,7 +2268,7 @@
       <c r="K119" s="3"/>
       <c r="L119" s="1"/>
     </row>
-    <row r="120" ht="13.8">
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="3" t="s">
         <v>147</v>
       </c>
@@ -2650,11 +2278,11 @@
       <c r="K120" s="3"/>
       <c r="L120" s="1"/>
     </row>
-    <row r="121" ht="13.8">
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F121" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H121" s="1">
+      <c r="H121" s="1" t="n">
         <v>60</v>
       </c>
       <c r="I121" s="6" t="s">
@@ -2663,12 +2291,10 @@
       <c r="J121" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="K121" s="3" t="s">
-        <v>238</v>
-      </c>
+      <c r="K121" s="3"/>
       <c r="L121" s="1"/>
     </row>
-    <row r="122" ht="13.8">
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="3" t="s">
         <v>147</v>
       </c>
@@ -2678,11 +2304,11 @@
       <c r="K122" s="3"/>
       <c r="L122" s="1"/>
     </row>
-    <row r="123" ht="13.8">
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F123" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H123" s="1" t="n">
         <v>61</v>
       </c>
       <c r="I123" s="8" t="s">
@@ -2691,16 +2317,14 @@
       <c r="J123" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="K123" s="3" t="s">
-        <v>239</v>
-      </c>
+      <c r="K123" s="3"/>
       <c r="L123" s="1"/>
     </row>
-    <row r="124" ht="13.8">
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F124" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H124" s="1" t="n">
         <v>62</v>
       </c>
       <c r="I124" s="8" t="s">
@@ -2709,16 +2333,14 @@
       <c r="J124" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="K124" s="3" t="s">
-        <v>240</v>
-      </c>
+      <c r="K124" s="3"/>
       <c r="L124" s="1"/>
     </row>
-    <row r="125" ht="13.8">
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F125" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H125" s="1">
+      <c r="H125" s="1" t="n">
         <v>63</v>
       </c>
       <c r="I125" s="6" t="s">
@@ -2727,17 +2349,15 @@
       <c r="J125" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="K125" s="3" t="s">
-        <v>241</v>
-      </c>
+      <c r="K125" s="3"/>
       <c r="L125" s="1"/>
     </row>
-    <row r="126" ht="13.8">
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E126" s="3"/>
       <c r="F126" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H126" s="1">
+      <c r="H126" s="1" t="n">
         <v>64</v>
       </c>
       <c r="I126" s="6" t="s">
@@ -2746,16 +2366,14 @@
       <c r="J126" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K126" s="3" t="s">
-        <v>242</v>
-      </c>
+      <c r="K126" s="3"/>
       <c r="L126" s="1"/>
     </row>
-    <row r="127" ht="13.8">
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F127" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H127" s="1">
+      <c r="H127" s="1" t="n">
         <v>65</v>
       </c>
       <c r="I127" s="6" t="s">
@@ -2764,17 +2382,15 @@
       <c r="J127" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="K127" s="3" t="s">
-        <v>243</v>
-      </c>
+      <c r="K127" s="3"/>
       <c r="L127" s="1"/>
     </row>
-    <row r="128" ht="35.05">
+    <row r="128" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E128" s="3"/>
       <c r="F128" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H128" s="1">
+      <c r="H128" s="1" t="n">
         <v>66</v>
       </c>
       <c r="I128" s="8" t="s">
@@ -2783,17 +2399,15 @@
       <c r="J128" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="K128" s="3" t="s">
-        <v>244</v>
-      </c>
+      <c r="K128" s="3"/>
       <c r="L128" s="1"/>
     </row>
-    <row r="129" ht="13.8">
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E129" s="3"/>
       <c r="F129" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H129" s="1">
+      <c r="H129" s="1" t="n">
         <v>67</v>
       </c>
       <c r="I129" s="8" t="s">
@@ -2802,12 +2416,10 @@
       <c r="J129" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K129" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="K129" s="3"/>
       <c r="L129" s="1"/>
     </row>
-    <row r="130" ht="13.8">
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="1" t="s">
         <v>134</v>
       </c>
@@ -2820,9 +2432,9 @@
       <c r="K130" s="3"/>
       <c r="L130" s="1"/>
     </row>
-    <row r="131" ht="13.8">
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F131" s="3"/>
-      <c r="H131" s="1">
+      <c r="H131" s="1" t="n">
         <v>68</v>
       </c>
       <c r="I131" s="6" t="s">
@@ -2831,12 +2443,10 @@
       <c r="J131" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="K131" s="3" t="s">
-        <v>245</v>
-      </c>
+      <c r="K131" s="3"/>
       <c r="L131" s="1"/>
     </row>
-    <row r="132" ht="12.8">
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="1" t="s">
         <v>66</v>
       </c>
@@ -2844,7 +2454,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="133" ht="12.8">
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D133" s="1" t="s">
         <v>68</v>
       </c>
@@ -2852,18 +2462,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="134" ht="12.8">
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D134" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E134" s="1">
+      <c r="E134" s="1" t="n">
         <v>74</v>
       </c>
       <c r="I134" s="3"/>
     </row>
-    <row r="135" ht="13.8">
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F135" s="3"/>
-      <c r="H135" s="1">
+      <c r="H135" s="1" t="n">
         <v>69</v>
       </c>
       <c r="I135" s="8" t="s">
@@ -2872,14 +2482,12 @@
       <c r="J135" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="K135" s="3" t="s">
-        <v>246</v>
-      </c>
+      <c r="K135" s="3"/>
       <c r="L135" s="1"/>
     </row>
-    <row r="136" ht="23.85">
+    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F136" s="3"/>
-      <c r="H136" s="1">
+      <c r="H136" s="1" t="n">
         <v>70</v>
       </c>
       <c r="I136" s="8" t="s">
@@ -2888,14 +2496,12 @@
       <c r="J136" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="K136" s="3" t="s">
-        <v>247</v>
-      </c>
+      <c r="K136" s="3"/>
       <c r="L136" s="1"/>
     </row>
-    <row r="137" ht="46.25">
+    <row r="137" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F137" s="3"/>
-      <c r="H137" s="1">
+      <c r="H137" s="1" t="n">
         <v>71</v>
       </c>
       <c r="I137" s="8" t="s">
@@ -2904,16 +2510,14 @@
       <c r="J137" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="K137" s="3" t="s">
-        <v>248</v>
-      </c>
+      <c r="K137" s="3"/>
       <c r="L137" s="1"/>
     </row>
-    <row r="138" ht="13.8">
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D138" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E138" s="1">
+      <c r="E138" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I138" s="6"/>
@@ -2921,30 +2525,30 @@
       <c r="K138" s="7"/>
       <c r="L138" s="1"/>
     </row>
-    <row r="139" ht="12.8">
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D139" s="1" t="s">
         <v>122</v>
       </c>
       <c r="L139" s="1"/>
     </row>
-    <row r="140" ht="12.8">
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D140" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I140" s="3"/>
       <c r="L140" s="1"/>
     </row>
-    <row r="141" ht="12.8">
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J141" s="3"/>
       <c r="L141" s="1"/>
     </row>
-    <row r="143" ht="12.8">
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
         <v>170</v>
       </c>
       <c r="L143" s="1"/>
     </row>
-    <row r="144" ht="12.8">
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D144" s="1" t="s">
         <v>11</v>
       </c>
@@ -2953,7 +2557,7 @@
       </c>
       <c r="L144" s="1"/>
     </row>
-    <row r="145" ht="12.8">
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D145" s="1" t="s">
         <v>11</v>
       </c>
@@ -2962,7 +2566,7 @@
       </c>
       <c r="L145" s="1"/>
     </row>
-    <row r="146" ht="12.8">
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D146" s="1" t="s">
         <v>78</v>
       </c>
@@ -2971,19 +2575,19 @@
       </c>
       <c r="L146" s="1"/>
     </row>
-    <row r="147" ht="13.8">
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D147" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E147" s="1">
+      <c r="E147" s="1" t="n">
         <v>74</v>
       </c>
       <c r="J147" s="6"/>
       <c r="K147" s="7"/>
       <c r="L147" s="1"/>
     </row>
-    <row r="148" ht="13.8">
-      <c r="H148" s="6">
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H148" s="6" t="n">
         <v>80</v>
       </c>
       <c r="I148" s="8" t="s">
@@ -2992,16 +2596,14 @@
       <c r="J148" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K148" s="7" t="s">
-        <v>249</v>
-      </c>
+      <c r="K148" s="7"/>
       <c r="L148" s="1"/>
     </row>
-    <row r="149" ht="13.8">
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F149" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H149" s="6">
+      <c r="H149" s="6" t="n">
         <v>81</v>
       </c>
       <c r="I149" s="8" t="s">
@@ -3010,13 +2612,11 @@
       <c r="J149" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="K149" s="7" t="s">
-        <v>250</v>
-      </c>
+      <c r="K149" s="7"/>
       <c r="L149" s="1"/>
     </row>
-    <row r="150" ht="13.8">
-      <c r="H150" s="6">
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H150" s="6" t="n">
         <v>82</v>
       </c>
       <c r="I150" s="8" t="s">
@@ -3025,18 +2625,16 @@
       <c r="J150" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="K150" s="7" t="s">
-        <v>251</v>
-      </c>
+      <c r="K150" s="7"/>
       <c r="L150" s="1"/>
     </row>
-    <row r="151" ht="13.8">
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D151" s="3"/>
       <c r="E151" s="15"/>
       <c r="F151" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H151" s="6">
+      <c r="H151" s="6" t="n">
         <v>83</v>
       </c>
       <c r="I151" s="8" t="s">
@@ -3045,16 +2643,14 @@
       <c r="J151" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="K151" s="7" t="s">
-        <v>252</v>
-      </c>
+      <c r="K151" s="7"/>
       <c r="L151" s="1"/>
     </row>
-    <row r="152" ht="56.7">
+    <row r="152" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F152" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H152" s="6">
+      <c r="H152" s="6" t="n">
         <v>84</v>
       </c>
       <c r="I152" s="8" t="s">
@@ -3063,14 +2659,12 @@
       <c r="J152" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="K152" s="7" t="s">
-        <v>253</v>
-      </c>
+      <c r="K152" s="7"/>
       <c r="L152" s="1"/>
     </row>
-    <row r="153" ht="23.85">
+    <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D153" s="3"/>
-      <c r="H153" s="6">
+      <c r="H153" s="6" t="n">
         <v>85</v>
       </c>
       <c r="I153" s="8" t="s">
@@ -3079,16 +2673,14 @@
       <c r="J153" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="K153" s="7" t="s">
-        <v>254</v>
-      </c>
+      <c r="K153" s="7"/>
       <c r="L153" s="1"/>
     </row>
-    <row r="154" ht="13.8">
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F154" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H154" s="6">
+      <c r="H154" s="6" t="n">
         <v>86</v>
       </c>
       <c r="I154" s="8" t="s">
@@ -3097,13 +2689,11 @@
       <c r="J154" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="K154" s="7" t="s">
-        <v>255</v>
-      </c>
+      <c r="K154" s="7"/>
       <c r="L154" s="1"/>
     </row>
-    <row r="155" ht="57.45">
-      <c r="H155" s="6">
+    <row r="155" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H155" s="6" t="n">
         <v>87</v>
       </c>
       <c r="I155" s="8" t="s">
@@ -3112,16 +2702,14 @@
       <c r="J155" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="K155" s="7" t="s">
-        <v>256</v>
-      </c>
+      <c r="K155" s="7"/>
       <c r="L155" s="1"/>
     </row>
-    <row r="156" ht="46.25">
+    <row r="156" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F156" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H156" s="6">
+      <c r="H156" s="6" t="n">
         <v>88</v>
       </c>
       <c r="I156" s="8" t="s">
@@ -3130,13 +2718,11 @@
       <c r="J156" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="K156" s="7" t="s">
-        <v>257</v>
-      </c>
+      <c r="K156" s="7"/>
       <c r="L156" s="1"/>
     </row>
-    <row r="157" ht="46.25">
-      <c r="H157" s="6">
+    <row r="157" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H157" s="6" t="n">
         <v>89</v>
       </c>
       <c r="I157" s="8" t="s">
@@ -3145,16 +2731,14 @@
       <c r="J157" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="K157" s="7" t="s">
-        <v>258</v>
-      </c>
+      <c r="K157" s="7"/>
       <c r="L157" s="1"/>
     </row>
-    <row r="158" ht="13.8">
+    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D158" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E158" s="1">
+      <c r="E158" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I158" s="6"/>
@@ -3162,13 +2746,13 @@
       <c r="K158" s="7"/>
       <c r="L158" s="1"/>
     </row>
-    <row r="159" ht="12.8">
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D159" s="1" t="s">
         <v>122</v>
       </c>
       <c r="L159" s="1"/>
     </row>
-    <row r="160" ht="12.8">
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D160" s="1" t="s">
         <v>22</v>
       </c>
@@ -3176,12 +2760,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I69 I73:I80 H5:H68 H70:H101 I102 I108 H144:H1048576 H103:H142 I143 I147:I157">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/farris.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/farris.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="farris" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="farris" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="259">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -402,7 +402,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">Eek!</t>
@@ -736,6 +736,246 @@
     <t xml:space="preserve">Demitas, the Exile... I wonder what he was like before he became...
 And what caused him to be exiled in the first place? One day, I’d love to hear his story from him.</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你好，#player大人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呜…呜呜…谁来…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呜呜…谁…谁在那里？　</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦哦…感谢仁慈的艾赫卡托尔赐予的机缘。
+我是奥尔维纳的歌手法莉斯。因为注意到了尼米尔的异变，雇佣冒险者一同来到这个洞穴，结果被凶暴化的魔物袭击陷入进退两难的地步。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作为将米西利亚传说传唱之人，我必须知道这片土地上发生了什么。但是，在这样的情况下，我只能回头……
+如果您还要继续前进的话，就把这条通道的钥匙交给您吧。我希望您能查明尼米尔深处的异变。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唉…附近有您的营地吗？
+我明白了。那我就暂且返回营地等您的消息。探索顺利完成后请跟我打声招呼。我有些话想跟您说。
+冒险家大人，祈愿您能平安归来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">您平安回来了呢。
+再次介绍…我是奥尔维娜的法莉斯，咏唱古老传说之人。就让我告诉您我所知道的一切关于尼米尔的事作为对您的报答吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">尼米尔…是提里斯上散落的遗迹之一，也是被称为风之墓场的洞窟。正如其名所述，这是一个回荡着悲哀风鸣的安稳洞窟……应该说…曾经是这样的。因为在十年战争之后，尼米尔就变了……
+尼米尔的森林开始枯萎，不再有风声，异形的魔物开始在地上徘徊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异变的原因…尼米尔的深层到底发生了什么呢？
+据传闻说，在洞窟的最下层沉睡着被遗忘众神的圣遗物。也许…我们是招来了古老神明的愤怒…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">―不，供奉在尼米尔最深处的并不是贵重的圣遗物，异变的原因也不是作祟。
+不好意思打断你讲话了。但是，那个洞窟的情况果然是和我们想的一样…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿什！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没事的，菲亚。让我说吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…十年战争和尼米尔的异变不是没有关系的。
+上次大战的事恐怕你也听说过了。东大陆，新王国耶鲁和沙漠帝国发起的战火不久便燃向各地，给世界带来了混乱。提里斯的国家也结成联盟进行了对抗，但在拥有萨伊拉飞艇的帝国面前简直就和婴儿一样。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在我们的土地被践踏的时候，我们的主公赛特拉斯大人对风诉说。结果尼米尔的天空中出现的一阵光之风化成的风暴袭击了帝国，被誉为无敌的萨伊拉的飞艇坠落到了米西利亚的土地上。
+…然后十年战争迎来了终结。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唤起「尼米尔狂风」的确实是赛特拉斯大人。但是，仅此而已吗？
+米西利亚刮起的光之风和尼米尔的异变之间，或许就是沉睡在被称为风之墓地尼米尔的「某物」回应了赛特拉斯大人的祈祷所致。
+我推测，那个神秘「某物」就藏在尼米尔的最深处。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现在阴云即将再次笼罩提里斯之上。
+帝国在重新磨锐折断的利爪，萨伊拉的舰队重建只是时间问题。在下一场战斗中，他们一定会为一雪前耻毫不留情地进行攻击。
+赛特拉斯大人对人类和艾莱亚的重新团结抱有希望，但如果米西利亚灭亡，那一切就无从说起了。为了生存，我们必须得到沉睡在尼米尔中的「力量」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…现在还不能说出一切，我们也并不了解一切。你一定会觉得是被卷入了麻烦的事情中吧。
+但是，你已经在此地定居，成为了米西利亚和提里斯的一员，这件事情和你也就并不是没有关系。
+所以呢，你就做好心理准备配合我们的调查吧。山洞里面也可能会有一两个宝贝，对你来说也不是坏事。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…话就说到这里吧。
+尼米尔的异变于我来说也不是毫无关系。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我打算暂时留在这里，观察事情的发展。
+冒险家大人，祝你武运亨通。希望你前进的道路上有风的加护。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#player大人，我有话跟您说。
+关于利萨纳斯，我也有线索。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的妹妹西奥露西亚在帕罗米亚王宫工作，从事历史研究。
+如果是她的话，一定可以从王宫图书馆所有的庞大资料中找到关于利萨纳斯的文献。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">从这里沿着路向西南方向走，有一个叫奥尔维纳的小村庄…那是我的故乡。
+西奥露西亚现在也应该回到村子里了。如果#player大人正在寻找利萨纳斯的线索，也许你可以去拜访她一次。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（嘀嘀咕咕）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">果然是…（嘀嘀咕咕）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊…！（嘀嘀咕咕）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你好啊，法莉斯小姐。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊，罗伊特尔大人。库罗茨亚正和我说到您的事情呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">噫。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊，不是……啊，库罗茨亚你要去哪里……等等啊……！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…罗伊特尔大人，对待这个年纪的少女，可不能看着人家的脸发出「噫」的声音啊…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不，我没有那样的意思！
+…只是，我想起了那个孩子眼睛的事情。法莉斯小姐也从凯特尔那里听说了吧？我被那个孩子讨厌了……没准哪天就突然没命了…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…罗伊特尔大人啊，我对你真是太失望了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明明不了解她拥有怎样的力量，却断言那是「诅咒」并恐惧着她…你难道不明白，这样的态度才最伤她的心吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没有什么但是！在害怕「诅咒」之前，你应该多想想那孩子与怎样的孤独战斗过。无论她有怎样的瞳色和过去，她也只是个少女。她也有心啊，罗伊特尔大人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法莉斯小姐…的确如你所言。
+其实，我也想和那个孩子好好相处。但却总是言多语失…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…库罗茨亚是个心思细腻老实的孩子。罗伊特尔大人是不是因为怕伤害到她而顾忌太多，才让事情毫无进展？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凡事都有过程。那些故事里的主人公们也是克服彼此间的隔阂才能建立真正相互信赖的关系。
+您知道吗，罗伊特尔大人。如果您想打开她的心扉，就必须用尽办法去直面她，引她说出真实的心声，然后全心全意地接纳她袒露出的灵魂呼喊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唔…嗯，感觉有点夸张，但我明白你的意思，法莉斯小姐。
+要引出库罗茨亚的心声吗…哎呀，这可真是个挑战呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#pc大人，您来的正好。
+那个…其实是这样，事情也过去这么久了，一直都没看到罗伊特尔大人有在还债的样子，大伙都想问问您的情况如何。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">罗伊特尔大人，请告诉我们…您宏伟的还债计划！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法莉斯小姐…根本就没有计划。
+…两千万奥伦这种荒唐的金额，我怎么还得起！ 我…我…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊！ 罗伊特尔大人！？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大家，罗伊特尔大人逃走了…！ 快，快点，抓住罗伊特尔大人！ 喂，凯特尔先生，您也快去追他！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯…好吧…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哈啊哈啊，可恶…怎么能让你们抓住我！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哈，这可是在开拓中锻炼出来的腰腿。只要我全力逃跑，区区女人和孩子…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…呜噶啊！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">歌罗贡，真是个好孩子！就这样拖住罗伊特尔！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哈啊…哈啊…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">快放弃吧，罗伊特尔。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你们…竟然联手…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">行吧行吧，其实我是有个还没完成的还款计划！
+我现在就去拿…请在这里等我。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊！ 罗伊特尔大人！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…逃跑…了呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然我觉得罗伊特尔大人即使身处困境也应该不会做出什么极端的行为…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但还是很担心呢。
+#pc大人，如果您对罗伊特尔大人的逃亡目的地有线索的话，能帮我找他吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（窃窃私语）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唔…（窃窃私语）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的意思是…（窃窃私语）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">什么，居然…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真是的，自从那个迪米塔斯来了之后，气氛一直都很沉重。库罗茨亚也变得不愿意说话了。
+他总是说些让人不安的话，真是让人头疼啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是罗伊特尔大人，我觉得他并不是什么坏人。迪米塔斯先生应该只是有心病吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯，心病？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虽然不能确信。但是，迪米塔斯先生的内心应该有些扭曲…
+那种诡异说话方式的背后，不知隐藏了多少苦恼和悲伤…真的让人很感兴趣。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…说起来，法莉斯小姐看着迪米塔斯时，眼神总是闪闪发光。
+他确实令人不快，但给人的印象并非纯粹的恶徒。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">流放者迪米塔斯…变成这样之前，他究竟是怎样的人呢。我也想知道他被「流放」的原因。
+…总有一天，我要听他本人来讲讲。</t>
+  </si>
 </sst>
 </file>
 
@@ -756,19 +996,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -788,7 +1028,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -814,7 +1054,7 @@
     <font>
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -833,7 +1073,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -842,94 +1082,94 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -943,13 +1183,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1125,24 +1365,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M160"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="63.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="73.45"/>
+    <col min="1" max="3" width="8.85" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
+    <col min="9" max="9" width="63.3" style="1" customWidth="1"/>
+    <col min="10" max="10" width="53.28" style="1" customWidth="1"/>
+    <col min="11" max="11" width="73.45" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1177,13 +1417,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H5:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H5:H1048576)</f>
         <v>89</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1191,7 +1431,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1199,18 +1439,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H12" s="1" t="n">
+    <row r="12" ht="12.8">
+      <c r="H12" s="1">
         <v>49</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -1219,8 +1459,11 @@
       <c r="J12" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" ht="12.8">
       <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1228,28 +1471,28 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H20" s="1" t="n">
+    <row r="20" ht="12.8">
+      <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -1258,19 +1501,22 @@
       <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H23" s="1" t="n">
+    <row r="23" ht="12.8">
+      <c r="H23" s="1">
         <v>2</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -1279,9 +1525,12 @@
       <c r="J23" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H24" s="1" t="n">
+      <c r="K23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" ht="64.15">
+      <c r="H24" s="1">
         <v>3</v>
       </c>
       <c r="I24" s="3" t="s">
@@ -1290,8 +1539,11 @@
       <c r="J24" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" ht="12.8">
       <c r="D25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1301,8 +1553,8 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="1" t="n">
+    <row r="26" ht="64.15">
+      <c r="H26" s="1">
         <v>4</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -1311,9 +1563,12 @@
       <c r="J26" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H27" s="1" t="n">
+      <c r="K26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" ht="64.15">
+      <c r="H27" s="1">
         <v>5</v>
       </c>
       <c r="I27" s="3" t="s">
@@ -1322,8 +1577,11 @@
       <c r="J27" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
       <c r="D28" s="1" t="s">
         <v>37</v>
       </c>
@@ -1331,18 +1589,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="D29" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.8">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H31" s="1" t="n">
+    <row r="31" ht="53.7">
+      <c r="H31" s="1">
         <v>6</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -1351,9 +1609,12 @@
       <c r="J31" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H32" s="1" t="n">
+      <c r="K31" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" ht="95.5">
+      <c r="H32" s="1">
         <v>7</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -1362,9 +1623,12 @@
       <c r="J32" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H33" s="1" t="n">
+      <c r="K32" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" ht="64.15">
+      <c r="H33" s="1">
         <v>8</v>
       </c>
       <c r="I33" s="3" t="s">
@@ -1373,8 +1637,11 @@
       <c r="J33" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" ht="12.8">
       <c r="D34" s="1" t="s">
         <v>46</v>
       </c>
@@ -1382,11 +1649,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="53.7">
       <c r="F35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="1" t="n">
+      <c r="H35" s="1">
         <v>9</v>
       </c>
       <c r="I35" s="3" t="s">
@@ -1395,12 +1662,15 @@
       <c r="J35" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" ht="12.8">
       <c r="F36" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="H36" s="1">
         <v>10</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -1409,12 +1679,15 @@
       <c r="J36" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K36" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="37" ht="12.8">
       <c r="F37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="1">
         <v>11</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -1423,8 +1696,11 @@
       <c r="J37" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K37" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
       <c r="D38" s="1" t="s">
         <v>54</v>
       </c>
@@ -1432,11 +1708,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="116.4">
       <c r="F39" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H39" s="1">
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
@@ -1445,12 +1721,15 @@
       <c r="J39" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" ht="74.6">
       <c r="F40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="H40" s="1">
         <v>13</v>
       </c>
       <c r="I40" s="3" t="s">
@@ -1459,12 +1738,15 @@
       <c r="J40" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" ht="95.5">
       <c r="F41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="H41" s="1">
         <v>14</v>
       </c>
       <c r="I41" s="3" t="s">
@@ -1473,12 +1755,15 @@
       <c r="J41" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" ht="105.95">
       <c r="F42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="H42" s="1">
         <v>15</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -1487,12 +1772,15 @@
       <c r="J42" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K42" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" ht="95.5">
       <c r="F43" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H43" s="1" t="n">
+      <c r="H43" s="1">
         <v>16</v>
       </c>
       <c r="I43" s="3" t="s">
@@ -1501,8 +1789,11 @@
       <c r="J43" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" ht="12.8">
       <c r="D44" s="1" t="s">
         <v>66</v>
       </c>
@@ -1510,7 +1801,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="D45" s="1" t="s">
         <v>68</v>
       </c>
@@ -1518,8 +1809,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H47" s="1" t="n">
+    <row r="47" ht="32.8">
+      <c r="H47" s="1">
         <v>17</v>
       </c>
       <c r="I47" s="3" t="s">
@@ -1528,9 +1819,12 @@
       <c r="J47" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H48" s="1" t="n">
+      <c r="K47" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="48" ht="43.25">
+      <c r="H48" s="1">
         <v>18</v>
       </c>
       <c r="I48" s="3" t="s">
@@ -1539,8 +1833,11 @@
       <c r="J48" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" ht="12.8">
       <c r="D49" s="1" t="s">
         <v>46</v>
       </c>
@@ -1548,7 +1845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="D50" s="1" t="s">
         <v>37</v>
       </c>
@@ -1556,41 +1853,50 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.8">
       <c r="D51" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="12.8">
       <c r="A57" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H61" s="1" t="n">
+    <row r="61" ht="32.8">
+      <c r="H61" s="1">
         <v>19</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H62" s="1" t="n">
+      <c r="K61" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" ht="43.25">
+      <c r="H62" s="1">
         <v>20</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H63" s="1" t="n">
+      <c r="K62" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" ht="53.7">
+      <c r="H63" s="1">
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K63" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65" ht="12.8">
       <c r="D65" s="1" t="s">
         <v>78</v>
       </c>
@@ -1598,18 +1904,18 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.8">
       <c r="D67" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="12.8">
       <c r="A69" s="1" t="s">
         <v>80</v>
       </c>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
       <c r="D70" s="1" t="s">
         <v>11</v>
       </c>
@@ -1618,7 +1924,7 @@
       </c>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.8">
       <c r="D71" s="1" t="s">
         <v>11</v>
       </c>
@@ -1627,7 +1933,7 @@
       </c>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="12.8">
       <c r="D72" s="1" t="s">
         <v>78</v>
       </c>
@@ -1636,19 +1942,19 @@
       </c>
       <c r="L72" s="1"/>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="13.8">
       <c r="D73" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="1">
         <v>74</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="7"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H74" s="6" t="n">
+    <row r="74" ht="13.8">
+      <c r="H74" s="6">
         <v>22</v>
       </c>
       <c r="I74" s="8" t="s">
@@ -1657,14 +1963,16 @@
       <c r="J74" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K74" s="7"/>
+      <c r="K74" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="13.8">
       <c r="F75" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H75" s="6" t="n">
+      <c r="H75" s="6">
         <v>23</v>
       </c>
       <c r="I75" s="8" t="s">
@@ -1673,11 +1981,13 @@
       <c r="J75" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K75" s="7"/>
+      <c r="K75" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H76" s="6" t="n">
+    <row r="76" ht="13.8">
+      <c r="H76" s="6">
         <v>24</v>
       </c>
       <c r="I76" s="8" t="s">
@@ -1686,14 +1996,16 @@
       <c r="J76" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="K76" s="7"/>
+      <c r="K76" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="13.8">
       <c r="F77" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H77" s="6" t="n">
+      <c r="H77" s="6">
         <v>25</v>
       </c>
       <c r="I77" s="8" t="s">
@@ -1702,11 +2014,13 @@
       <c r="J77" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K77" s="7"/>
+      <c r="K77" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H78" s="6" t="n">
+    <row r="78" ht="13.8">
+      <c r="H78" s="6">
         <v>26</v>
       </c>
       <c r="I78" s="8" t="s">
@@ -1715,14 +2029,16 @@
       <c r="J78" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="K78" s="7"/>
+      <c r="K78" s="7" t="s">
+        <v>215</v>
+      </c>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="13.8">
       <c r="F79" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H79" s="6" t="n">
+      <c r="H79" s="6">
         <v>27</v>
       </c>
       <c r="I79" s="8" t="s">
@@ -1731,11 +2047,13 @@
       <c r="J79" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="K79" s="7"/>
+      <c r="K79" s="7" t="s">
+        <v>216</v>
+      </c>
       <c r="L79" s="1"/>
     </row>
-    <row r="80" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H80" s="11" t="n">
+    <row r="80" ht="25.35">
+      <c r="H80" s="11">
         <v>28</v>
       </c>
       <c r="I80" s="12" t="s">
@@ -1744,14 +2062,16 @@
       <c r="J80" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="K80" s="3"/>
+      <c r="K80" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="L80" s="1"/>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="13.8">
       <c r="F81" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H81" s="1" t="n">
+      <c r="H81" s="1">
         <v>29</v>
       </c>
       <c r="I81" s="12" t="s">
@@ -1760,14 +2080,16 @@
       <c r="J81" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K81" s="3"/>
+      <c r="K81" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="L81" s="1"/>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" ht="13.8">
       <c r="F82" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="H82" s="1">
         <v>30</v>
       </c>
       <c r="I82" s="12" t="s">
@@ -1776,14 +2098,16 @@
       <c r="J82" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="K82" s="7"/>
+      <c r="K82" s="7" t="s">
+        <v>218</v>
+      </c>
       <c r="L82" s="1"/>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="13.8">
       <c r="F83" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H83" s="1" t="n">
+      <c r="H83" s="1">
         <v>31</v>
       </c>
       <c r="I83" s="12" t="s">
@@ -1792,14 +2116,16 @@
       <c r="J83" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="K83" s="3"/>
+      <c r="K83" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="L83" s="1"/>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="13.8">
       <c r="F84" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H84" s="1" t="n">
+      <c r="H84" s="1">
         <v>32</v>
       </c>
       <c r="I84" s="12" t="s">
@@ -1808,12 +2134,14 @@
       <c r="J84" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="K84" s="3"/>
+      <c r="K84" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H85" s="1" t="n">
+    <row r="85" ht="13.8">
+      <c r="H85" s="1">
         <v>33</v>
       </c>
       <c r="I85" s="12" t="s">
@@ -1822,14 +2150,16 @@
       <c r="J85" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="K85" s="3"/>
+      <c r="K85" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="L85" s="1"/>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="13.8">
       <c r="F86" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H86" s="1" t="n">
+      <c r="H86" s="1">
         <v>34</v>
       </c>
       <c r="I86" s="12" t="s">
@@ -1838,11 +2168,13 @@
       <c r="J86" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K86" s="3"/>
+      <c r="K86" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="L86" s="1"/>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H87" s="1" t="n">
+    <row r="87" ht="13.8">
+      <c r="H87" s="1">
         <v>35</v>
       </c>
       <c r="I87" s="8" t="s">
@@ -1851,14 +2183,16 @@
       <c r="J87" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="K87" s="3"/>
+      <c r="K87" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="L87" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="57.45">
       <c r="F88" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H88" s="1" t="n">
+      <c r="H88" s="1">
         <v>36</v>
       </c>
       <c r="I88" s="8" t="s">
@@ -1867,11 +2201,13 @@
       <c r="J88" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="K88" s="3"/>
+      <c r="K88" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="L88" s="1"/>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H89" s="1" t="n">
+    <row r="89" ht="13.8">
+      <c r="H89" s="1">
         <v>37</v>
       </c>
       <c r="I89" s="8" t="s">
@@ -1880,11 +2216,13 @@
       <c r="J89" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="K89" s="3"/>
+      <c r="K89" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="L89" s="1"/>
     </row>
-    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H90" s="1" t="n">
+    <row r="90" ht="35.05">
+      <c r="H90" s="1">
         <v>38</v>
       </c>
       <c r="I90" s="8" t="s">
@@ -1893,14 +2231,16 @@
       <c r="J90" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K90" s="3"/>
+      <c r="K90" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="L90" s="1"/>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="13.8">
       <c r="F91" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H91" s="1" t="n">
+      <c r="H91" s="1">
         <v>39</v>
       </c>
       <c r="I91" s="8" t="s">
@@ -1909,11 +2249,13 @@
       <c r="J91" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K91" s="3"/>
+      <c r="K91" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="L91" s="1"/>
     </row>
-    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H92" s="1" t="n">
+    <row r="92" ht="35.05">
+      <c r="H92" s="1">
         <v>40</v>
       </c>
       <c r="I92" s="8" t="s">
@@ -1922,14 +2264,16 @@
       <c r="J92" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="K92" s="3"/>
+      <c r="K92" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="L92" s="1"/>
     </row>
-    <row r="93" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" ht="46.25">
       <c r="F93" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H93" s="1" t="n">
+      <c r="H93" s="1">
         <v>41</v>
       </c>
       <c r="I93" s="8" t="s">
@@ -1938,18 +2282,20 @@
       <c r="J93" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="K93" s="3"/>
+      <c r="K93" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="L93" s="1"/>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="13.8">
       <c r="F94" s="3"/>
       <c r="I94" s="8"/>
       <c r="J94" s="10"/>
       <c r="K94" s="3"/>
       <c r="L94" s="1"/>
     </row>
-    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H95" s="1" t="n">
+    <row r="95" ht="23.85">
+      <c r="H95" s="1">
         <v>43</v>
       </c>
       <c r="I95" s="8" t="s">
@@ -1958,11 +2304,13 @@
       <c r="J95" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="K95" s="3"/>
+      <c r="K95" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="L95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H96" s="1" t="n">
+    <row r="96" ht="69.4">
+      <c r="H96" s="1">
         <v>48</v>
       </c>
       <c r="I96" s="8" t="s">
@@ -1971,14 +2319,16 @@
       <c r="J96" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="K96" s="3"/>
+      <c r="K96" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="L96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" ht="56.7">
       <c r="F97" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="H97" s="1">
         <v>44</v>
       </c>
       <c r="I97" s="8" t="s">
@@ -1987,14 +2337,16 @@
       <c r="J97" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="K97" s="3"/>
+      <c r="K97" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="L97" s="1"/>
     </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" ht="13.8">
       <c r="D98" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E98" s="1" t="n">
+      <c r="E98" s="1">
         <v>3</v>
       </c>
       <c r="I98" s="6"/>
@@ -2002,28 +2354,28 @@
       <c r="K98" s="7"/>
       <c r="L98" s="1"/>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" ht="12.8">
       <c r="D99" s="1" t="s">
         <v>122</v>
       </c>
       <c r="L99" s="1"/>
     </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" ht="12.8">
       <c r="D100" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L100" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" ht="12.8">
       <c r="L101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" ht="12.8">
       <c r="A102" s="1" t="s">
         <v>123</v>
       </c>
       <c r="L102" s="1"/>
     </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" ht="12.8">
       <c r="D103" s="1" t="s">
         <v>11</v>
       </c>
@@ -2032,7 +2384,7 @@
       </c>
       <c r="L103" s="1"/>
     </row>
-    <row r="104" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" s="1" customFormat="1" ht="12.8">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -2049,7 +2401,7 @@
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
     </row>
-    <row r="105" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" s="1" customFormat="1" ht="12.8">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -2066,7 +2418,7 @@
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
     </row>
-    <row r="106" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" s="1" customFormat="1" ht="12.8">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -2083,7 +2435,7 @@
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" ht="12.8">
       <c r="D107" s="1" t="s">
         <v>78</v>
       </c>
@@ -2092,20 +2444,20 @@
       </c>
       <c r="L107" s="1"/>
     </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" ht="13.8">
       <c r="D108" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E108" s="1" t="n">
+      <c r="E108" s="1">
         <v>72</v>
       </c>
       <c r="J108" s="6"/>
       <c r="K108" s="7"/>
       <c r="L108" s="1"/>
     </row>
-    <row r="109" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" ht="49.25">
       <c r="F109" s="3"/>
-      <c r="H109" s="1" t="n">
+      <c r="H109" s="1">
         <v>50</v>
       </c>
       <c r="I109" s="12" t="s">
@@ -2114,12 +2466,14 @@
       <c r="J109" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="K109" s="3"/>
+      <c r="K109" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="L109" s="1"/>
     </row>
-    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" ht="23.85">
       <c r="F110" s="3"/>
-      <c r="H110" s="1" t="n">
+      <c r="H110" s="1">
         <v>51</v>
       </c>
       <c r="I110" s="8" t="s">
@@ -2128,14 +2482,16 @@
       <c r="J110" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K110" s="3"/>
+      <c r="K110" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="L110" s="1"/>
     </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" ht="13.8">
       <c r="F111" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H111" s="1" t="n">
+      <c r="H111" s="1">
         <v>52</v>
       </c>
       <c r="I111" s="8" t="s">
@@ -2144,14 +2500,16 @@
       <c r="J111" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K111" s="3"/>
+      <c r="K111" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="L111" s="1"/>
     </row>
-    <row r="112" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" ht="45.5">
       <c r="F112" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H112" s="1" t="n">
+      <c r="H112" s="1">
         <v>53</v>
       </c>
       <c r="I112" s="8" t="s">
@@ -2160,10 +2518,12 @@
       <c r="J112" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="K112" s="3"/>
+      <c r="K112" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="L112" s="1"/>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" ht="13.8">
       <c r="D113" s="1" t="s">
         <v>134</v>
       </c>
@@ -2171,17 +2531,19 @@
         <v>135</v>
       </c>
       <c r="F113" s="3"/>
-      <c r="H113" s="1" t="n">
+      <c r="H113" s="1">
         <v>54</v>
       </c>
       <c r="I113" s="11"/>
       <c r="J113" s="10"/>
-      <c r="K113" s="3"/>
+      <c r="K113" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="L113" s="1"/>
     </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" ht="13.8">
       <c r="F114" s="3"/>
-      <c r="H114" s="1" t="n">
+      <c r="H114" s="1">
         <v>55</v>
       </c>
       <c r="I114" s="6" t="s">
@@ -2190,12 +2552,14 @@
       <c r="J114" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="K114" s="3"/>
+      <c r="K114" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="L114" s="1"/>
     </row>
-    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" ht="23.85">
       <c r="F115" s="3"/>
-      <c r="H115" s="1" t="n">
+      <c r="H115" s="1">
         <v>56</v>
       </c>
       <c r="I115" s="8" t="s">
@@ -2204,14 +2568,16 @@
       <c r="J115" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="K115" s="3"/>
+      <c r="K115" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="L115" s="1"/>
     </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" ht="13.8">
       <c r="F116" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H116" s="1" t="n">
+      <c r="H116" s="1">
         <v>57</v>
       </c>
       <c r="I116" s="6" t="s">
@@ -2220,14 +2586,16 @@
       <c r="J116" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="K116" s="3"/>
+      <c r="K116" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="L116" s="1"/>
     </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" ht="13.8">
       <c r="F117" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H117" s="1" t="n">
+      <c r="H117" s="1">
         <v>58</v>
       </c>
       <c r="I117" s="6" t="s">
@@ -2236,14 +2604,16 @@
       <c r="J117" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="K117" s="3"/>
+      <c r="K117" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="L117" s="1"/>
     </row>
-    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" ht="23.85">
       <c r="F118" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H118" s="1" t="n">
+      <c r="H118" s="1">
         <v>59</v>
       </c>
       <c r="I118" s="6" t="s">
@@ -2252,10 +2622,12 @@
       <c r="J118" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="K118" s="3"/>
+      <c r="K118" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="L118" s="1"/>
     </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" ht="13.8">
       <c r="D119" s="1" t="s">
         <v>134</v>
       </c>
@@ -2268,7 +2640,7 @@
       <c r="K119" s="3"/>
       <c r="L119" s="1"/>
     </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" ht="13.8">
       <c r="D120" s="3" t="s">
         <v>147</v>
       </c>
@@ -2278,11 +2650,11 @@
       <c r="K120" s="3"/>
       <c r="L120" s="1"/>
     </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" ht="13.8">
       <c r="F121" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H121" s="1" t="n">
+      <c r="H121" s="1">
         <v>60</v>
       </c>
       <c r="I121" s="6" t="s">
@@ -2291,10 +2663,12 @@
       <c r="J121" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="K121" s="3"/>
+      <c r="K121" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="L121" s="1"/>
     </row>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" ht="13.8">
       <c r="D122" s="3" t="s">
         <v>147</v>
       </c>
@@ -2304,11 +2678,11 @@
       <c r="K122" s="3"/>
       <c r="L122" s="1"/>
     </row>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" ht="13.8">
       <c r="F123" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H123" s="1" t="n">
+      <c r="H123" s="1">
         <v>61</v>
       </c>
       <c r="I123" s="8" t="s">
@@ -2317,14 +2691,16 @@
       <c r="J123" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="K123" s="3"/>
+      <c r="K123" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="L123" s="1"/>
     </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" ht="13.8">
       <c r="F124" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H124" s="1" t="n">
+      <c r="H124" s="1">
         <v>62</v>
       </c>
       <c r="I124" s="8" t="s">
@@ -2333,14 +2709,16 @@
       <c r="J124" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="K124" s="3"/>
+      <c r="K124" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="L124" s="1"/>
     </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" ht="13.8">
       <c r="F125" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="H125" s="1">
         <v>63</v>
       </c>
       <c r="I125" s="6" t="s">
@@ -2349,15 +2727,17 @@
       <c r="J125" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="K125" s="3"/>
+      <c r="K125" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="L125" s="1"/>
     </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" ht="13.8">
       <c r="E126" s="3"/>
       <c r="F126" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H126" s="1" t="n">
+      <c r="H126" s="1">
         <v>64</v>
       </c>
       <c r="I126" s="6" t="s">
@@ -2366,14 +2746,16 @@
       <c r="J126" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K126" s="3"/>
+      <c r="K126" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="L126" s="1"/>
     </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" ht="13.8">
       <c r="F127" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H127" s="1" t="n">
+      <c r="H127" s="1">
         <v>65</v>
       </c>
       <c r="I127" s="6" t="s">
@@ -2382,15 +2764,17 @@
       <c r="J127" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="K127" s="3"/>
+      <c r="K127" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="L127" s="1"/>
     </row>
-    <row r="128" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" ht="35.05">
       <c r="E128" s="3"/>
       <c r="F128" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H128" s="1" t="n">
+      <c r="H128" s="1">
         <v>66</v>
       </c>
       <c r="I128" s="8" t="s">
@@ -2399,15 +2783,17 @@
       <c r="J128" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="K128" s="3"/>
+      <c r="K128" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="L128" s="1"/>
     </row>
-    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" ht="13.8">
       <c r="E129" s="3"/>
       <c r="F129" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H129" s="1" t="n">
+      <c r="H129" s="1">
         <v>67</v>
       </c>
       <c r="I129" s="8" t="s">
@@ -2416,10 +2802,12 @@
       <c r="J129" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K129" s="3"/>
+      <c r="K129" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="L129" s="1"/>
     </row>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" ht="13.8">
       <c r="D130" s="1" t="s">
         <v>134</v>
       </c>
@@ -2432,9 +2820,9 @@
       <c r="K130" s="3"/>
       <c r="L130" s="1"/>
     </row>
-    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="13.8">
       <c r="F131" s="3"/>
-      <c r="H131" s="1" t="n">
+      <c r="H131" s="1">
         <v>68</v>
       </c>
       <c r="I131" s="6" t="s">
@@ -2443,10 +2831,12 @@
       <c r="J131" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="K131" s="3"/>
+      <c r="K131" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="L131" s="1"/>
     </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" ht="12.8">
       <c r="D132" s="1" t="s">
         <v>66</v>
       </c>
@@ -2454,7 +2844,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" ht="12.8">
       <c r="D133" s="1" t="s">
         <v>68</v>
       </c>
@@ -2462,18 +2852,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" ht="12.8">
       <c r="D134" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E134" s="1" t="n">
+      <c r="E134" s="1">
         <v>74</v>
       </c>
       <c r="I134" s="3"/>
     </row>
-    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" ht="13.8">
       <c r="F135" s="3"/>
-      <c r="H135" s="1" t="n">
+      <c r="H135" s="1">
         <v>69</v>
       </c>
       <c r="I135" s="8" t="s">
@@ -2482,12 +2872,14 @@
       <c r="J135" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="K135" s="3"/>
+      <c r="K135" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="L135" s="1"/>
     </row>
-    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" ht="23.85">
       <c r="F136" s="3"/>
-      <c r="H136" s="1" t="n">
+      <c r="H136" s="1">
         <v>70</v>
       </c>
       <c r="I136" s="8" t="s">
@@ -2496,12 +2888,14 @@
       <c r="J136" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="K136" s="3"/>
+      <c r="K136" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="L136" s="1"/>
     </row>
-    <row r="137" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" ht="46.25">
       <c r="F137" s="3"/>
-      <c r="H137" s="1" t="n">
+      <c r="H137" s="1">
         <v>71</v>
       </c>
       <c r="I137" s="8" t="s">
@@ -2510,14 +2904,16 @@
       <c r="J137" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="K137" s="3"/>
+      <c r="K137" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="L137" s="1"/>
     </row>
-    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" ht="13.8">
       <c r="D138" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E138" s="1" t="n">
+      <c r="E138" s="1">
         <v>3</v>
       </c>
       <c r="I138" s="6"/>
@@ -2525,30 +2921,30 @@
       <c r="K138" s="7"/>
       <c r="L138" s="1"/>
     </row>
-    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" ht="12.8">
       <c r="D139" s="1" t="s">
         <v>122</v>
       </c>
       <c r="L139" s="1"/>
     </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" ht="12.8">
       <c r="D140" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I140" s="3"/>
       <c r="L140" s="1"/>
     </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" ht="12.8">
       <c r="J141" s="3"/>
       <c r="L141" s="1"/>
     </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" ht="12.8">
       <c r="A143" s="1" t="s">
         <v>170</v>
       </c>
       <c r="L143" s="1"/>
     </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" ht="12.8">
       <c r="D144" s="1" t="s">
         <v>11</v>
       </c>
@@ -2557,7 +2953,7 @@
       </c>
       <c r="L144" s="1"/>
     </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" ht="12.8">
       <c r="D145" s="1" t="s">
         <v>11</v>
       </c>
@@ -2566,7 +2962,7 @@
       </c>
       <c r="L145" s="1"/>
     </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" ht="12.8">
       <c r="D146" s="1" t="s">
         <v>78</v>
       </c>
@@ -2575,19 +2971,19 @@
       </c>
       <c r="L146" s="1"/>
     </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" ht="13.8">
       <c r="D147" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E147" s="1" t="n">
+      <c r="E147" s="1">
         <v>74</v>
       </c>
       <c r="J147" s="6"/>
       <c r="K147" s="7"/>
       <c r="L147" s="1"/>
     </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H148" s="6" t="n">
+    <row r="148" ht="13.8">
+      <c r="H148" s="6">
         <v>80</v>
       </c>
       <c r="I148" s="8" t="s">
@@ -2596,14 +2992,16 @@
       <c r="J148" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K148" s="7"/>
+      <c r="K148" s="7" t="s">
+        <v>249</v>
+      </c>
       <c r="L148" s="1"/>
     </row>
-    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" ht="13.8">
       <c r="F149" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H149" s="6" t="n">
+      <c r="H149" s="6">
         <v>81</v>
       </c>
       <c r="I149" s="8" t="s">
@@ -2612,11 +3010,13 @@
       <c r="J149" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="K149" s="7"/>
+      <c r="K149" s="7" t="s">
+        <v>250</v>
+      </c>
       <c r="L149" s="1"/>
     </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H150" s="6" t="n">
+    <row r="150" ht="13.8">
+      <c r="H150" s="6">
         <v>82</v>
       </c>
       <c r="I150" s="8" t="s">
@@ -2625,16 +3025,18 @@
       <c r="J150" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="K150" s="7"/>
+      <c r="K150" s="7" t="s">
+        <v>251</v>
+      </c>
       <c r="L150" s="1"/>
     </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" ht="13.8">
       <c r="D151" s="3"/>
       <c r="E151" s="15"/>
       <c r="F151" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H151" s="6" t="n">
+      <c r="H151" s="6">
         <v>83</v>
       </c>
       <c r="I151" s="8" t="s">
@@ -2643,14 +3045,16 @@
       <c r="J151" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="K151" s="7"/>
+      <c r="K151" s="7" t="s">
+        <v>252</v>
+      </c>
       <c r="L151" s="1"/>
     </row>
-    <row r="152" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" ht="56.7">
       <c r="F152" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H152" s="6" t="n">
+      <c r="H152" s="6">
         <v>84</v>
       </c>
       <c r="I152" s="8" t="s">
@@ -2659,12 +3063,14 @@
       <c r="J152" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="K152" s="7"/>
+      <c r="K152" s="7" t="s">
+        <v>253</v>
+      </c>
       <c r="L152" s="1"/>
     </row>
-    <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" ht="23.85">
       <c r="D153" s="3"/>
-      <c r="H153" s="6" t="n">
+      <c r="H153" s="6">
         <v>85</v>
       </c>
       <c r="I153" s="8" t="s">
@@ -2673,14 +3079,16 @@
       <c r="J153" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="K153" s="7"/>
+      <c r="K153" s="7" t="s">
+        <v>254</v>
+      </c>
       <c r="L153" s="1"/>
     </row>
-    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" ht="13.8">
       <c r="F154" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H154" s="6" t="n">
+      <c r="H154" s="6">
         <v>86</v>
       </c>
       <c r="I154" s="8" t="s">
@@ -2689,11 +3097,13 @@
       <c r="J154" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="K154" s="7"/>
+      <c r="K154" s="7" t="s">
+        <v>255</v>
+      </c>
       <c r="L154" s="1"/>
     </row>
-    <row r="155" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H155" s="6" t="n">
+    <row r="155" ht="57.45">
+      <c r="H155" s="6">
         <v>87</v>
       </c>
       <c r="I155" s="8" t="s">
@@ -2702,14 +3112,16 @@
       <c r="J155" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="K155" s="7"/>
+      <c r="K155" s="7" t="s">
+        <v>256</v>
+      </c>
       <c r="L155" s="1"/>
     </row>
-    <row r="156" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" ht="46.25">
       <c r="F156" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H156" s="6" t="n">
+      <c r="H156" s="6">
         <v>88</v>
       </c>
       <c r="I156" s="8" t="s">
@@ -2718,11 +3130,13 @@
       <c r="J156" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="K156" s="7"/>
+      <c r="K156" s="7" t="s">
+        <v>257</v>
+      </c>
       <c r="L156" s="1"/>
     </row>
-    <row r="157" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H157" s="6" t="n">
+    <row r="157" ht="46.25">
+      <c r="H157" s="6">
         <v>89</v>
       </c>
       <c r="I157" s="8" t="s">
@@ -2731,14 +3145,16 @@
       <c r="J157" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="K157" s="7"/>
+      <c r="K157" s="7" t="s">
+        <v>258</v>
+      </c>
       <c r="L157" s="1"/>
     </row>
-    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" ht="13.8">
       <c r="D158" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E158" s="1" t="n">
+      <c r="E158" s="1">
         <v>3</v>
       </c>
       <c r="I158" s="6"/>
@@ -2746,13 +3162,13 @@
       <c r="K158" s="7"/>
       <c r="L158" s="1"/>
     </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" ht="12.8">
       <c r="D159" s="1" t="s">
         <v>122</v>
       </c>
       <c r="L159" s="1"/>
     </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" ht="12.8">
       <c r="D160" s="1" t="s">
         <v>22</v>
       </c>
@@ -2760,12 +3176,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I69 I73:I80 H5:H68 H70:H101 I102 I108 H144:H1048576 H103:H142 I143 I147:I157">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
